--- a/downloads/Trainory_GRC_Analytics_Dashboard.xlsx
+++ b/downloads/Trainory_GRC_Analytics_Dashboard.xlsx
@@ -2,14 +2,14 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Dashboard" sheetId="1" r:id="R4070fd0f6c654b7a"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Metrics" sheetId="2" r:id="R844fefe6e0f24150"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Risk Data" sheetId="3" r:id="R2b0b22315a314aa0"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Control Data" sheetId="4" r:id="R20a550d4bef94195"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Vendor Data" sheetId="5" r:id="Re4124f73bd384215"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Access Data" sheetId="6" r:id="R0c3490f298924ad8"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Findings Data" sheetId="7" r:id="R13d2377775dc4312"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Dashboard Guide" sheetId="8" r:id="R2db4cb0a13574e7f"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Dashboard" sheetId="1" r:id="R12bf213ec93b48af"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Metrics" sheetId="2" r:id="R911d8d8572f54634"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Risk Data" sheetId="3" r:id="R63dba513f2bc476d"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Control Data" sheetId="4" r:id="R3b459040fcb74061"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Vendor Data" sheetId="5" r:id="R985e198c39b648e2"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Access Data" sheetId="6" r:id="Ra1b0dffb56c24529"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Findings Data" sheetId="7" r:id="Rc2ac967731fb46eb"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Dashboard Guide" sheetId="8" r:id="R7bff48ccbb5f4f7b"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -729,7 +729,7 @@
         <x:color rgb="FF991B1B"/>
       </x:font>
       <x:fill>
-        <x:patternFill patternType="solid">
+        <x:patternFill>
           <x:bgColor rgb="FFFEE2E2"/>
         </x:patternFill>
       </x:fill>
@@ -740,7 +740,7 @@
         <x:color rgb="FF9A3412"/>
       </x:font>
       <x:fill>
-        <x:patternFill patternType="solid">
+        <x:patternFill>
           <x:bgColor rgb="FFFFEDD5"/>
         </x:patternFill>
       </x:fill>
@@ -750,7 +750,7 @@
         <x:color rgb="FF854D0E"/>
       </x:font>
       <x:fill>
-        <x:patternFill patternType="solid">
+        <x:patternFill>
           <x:bgColor rgb="FFFEF3C7"/>
         </x:patternFill>
       </x:fill>
@@ -760,7 +760,7 @@
         <x:color rgb="FF166534"/>
       </x:font>
       <x:fill>
-        <x:patternFill patternType="solid">
+        <x:patternFill>
           <x:bgColor rgb="FFDCFCE7"/>
         </x:patternFill>
       </x:fill>
@@ -770,7 +770,7 @@
         <x:color rgb="FF166534"/>
       </x:font>
       <x:fill>
-        <x:patternFill patternType="solid">
+        <x:patternFill>
           <x:bgColor rgb="FFDCFCE7"/>
         </x:patternFill>
       </x:fill>
@@ -780,7 +780,7 @@
         <x:color rgb="FF991B1B"/>
       </x:font>
       <x:fill>
-        <x:patternFill patternType="solid">
+        <x:patternFill>
           <x:bgColor rgb="FFFEE2E2"/>
         </x:patternFill>
       </x:fill>
@@ -791,7 +791,7 @@
         <x:color rgb="FF991B1B"/>
       </x:font>
       <x:fill>
-        <x:patternFill patternType="solid">
+        <x:patternFill>
           <x:bgColor rgb="FFFEE2E2"/>
         </x:patternFill>
       </x:fill>
@@ -802,7 +802,7 @@
         <x:color rgb="FF9A3412"/>
       </x:font>
       <x:fill>
-        <x:patternFill patternType="solid">
+        <x:patternFill>
           <x:bgColor rgb="FFFFEDD5"/>
         </x:patternFill>
       </x:fill>
@@ -812,7 +812,7 @@
         <x:color rgb="FF854D0E"/>
       </x:font>
       <x:fill>
-        <x:patternFill patternType="solid">
+        <x:patternFill>
           <x:bgColor rgb="FFFEF3C7"/>
         </x:patternFill>
       </x:fill>
@@ -822,7 +822,7 @@
         <x:color rgb="FF166534"/>
       </x:font>
       <x:fill>
-        <x:patternFill patternType="solid">
+        <x:patternFill>
           <x:bgColor rgb="FFDCFCE7"/>
         </x:patternFill>
       </x:fill>
@@ -832,7 +832,7 @@
         <x:color rgb="FF166534"/>
       </x:font>
       <x:fill>
-        <x:patternFill patternType="solid">
+        <x:patternFill>
           <x:bgColor rgb="FFDCFCE7"/>
         </x:patternFill>
       </x:fill>
@@ -842,7 +842,7 @@
         <x:color rgb="FF991B1B"/>
       </x:font>
       <x:fill>
-        <x:patternFill patternType="solid">
+        <x:patternFill>
           <x:bgColor rgb="FFFEE2E2"/>
         </x:patternFill>
       </x:fill>
@@ -853,7 +853,7 @@
         <x:color rgb="FF991B1B"/>
       </x:font>
       <x:fill>
-        <x:patternFill patternType="solid">
+        <x:patternFill>
           <x:bgColor rgb="FFFEE2E2"/>
         </x:patternFill>
       </x:fill>
@@ -864,7 +864,7 @@
         <x:color rgb="FF9A3412"/>
       </x:font>
       <x:fill>
-        <x:patternFill patternType="solid">
+        <x:patternFill>
           <x:bgColor rgb="FFFFEDD5"/>
         </x:patternFill>
       </x:fill>
@@ -874,7 +874,7 @@
         <x:color rgb="FF854D0E"/>
       </x:font>
       <x:fill>
-        <x:patternFill patternType="solid">
+        <x:patternFill>
           <x:bgColor rgb="FFFEF3C7"/>
         </x:patternFill>
       </x:fill>
@@ -884,7 +884,7 @@
         <x:color rgb="FF166534"/>
       </x:font>
       <x:fill>
-        <x:patternFill patternType="solid">
+        <x:patternFill>
           <x:bgColor rgb="FFDCFCE7"/>
         </x:patternFill>
       </x:fill>
@@ -894,7 +894,7 @@
         <x:color rgb="FF166534"/>
       </x:font>
       <x:fill>
-        <x:patternFill patternType="solid">
+        <x:patternFill>
           <x:bgColor rgb="FFDCFCE7"/>
         </x:patternFill>
       </x:fill>
@@ -904,7 +904,7 @@
         <x:color rgb="FF991B1B"/>
       </x:font>
       <x:fill>
-        <x:patternFill patternType="solid">
+        <x:patternFill>
           <x:bgColor rgb="FFFEE2E2"/>
         </x:patternFill>
       </x:fill>
@@ -915,7 +915,7 @@
         <x:color rgb="FF991B1B"/>
       </x:font>
       <x:fill>
-        <x:patternFill patternType="solid">
+        <x:patternFill>
           <x:bgColor rgb="FFFEE2E2"/>
         </x:patternFill>
       </x:fill>
@@ -926,7 +926,7 @@
         <x:color rgb="FF9A3412"/>
       </x:font>
       <x:fill>
-        <x:patternFill patternType="solid">
+        <x:patternFill>
           <x:bgColor rgb="FFFFEDD5"/>
         </x:patternFill>
       </x:fill>
@@ -936,7 +936,7 @@
         <x:color rgb="FF854D0E"/>
       </x:font>
       <x:fill>
-        <x:patternFill patternType="solid">
+        <x:patternFill>
           <x:bgColor rgb="FFFEF3C7"/>
         </x:patternFill>
       </x:fill>
@@ -946,7 +946,7 @@
         <x:color rgb="FF166534"/>
       </x:font>
       <x:fill>
-        <x:patternFill patternType="solid">
+        <x:patternFill>
           <x:bgColor rgb="FFDCFCE7"/>
         </x:patternFill>
       </x:fill>
@@ -956,7 +956,7 @@
         <x:color rgb="FF166534"/>
       </x:font>
       <x:fill>
-        <x:patternFill patternType="solid">
+        <x:patternFill>
           <x:bgColor rgb="FFDCFCE7"/>
         </x:patternFill>
       </x:fill>
@@ -966,7 +966,7 @@
         <x:color rgb="FF991B1B"/>
       </x:font>
       <x:fill>
-        <x:patternFill patternType="solid">
+        <x:patternFill>
           <x:bgColor rgb="FFFEE2E2"/>
         </x:patternFill>
       </x:fill>
@@ -977,7 +977,7 @@
         <x:color rgb="FF991B1B"/>
       </x:font>
       <x:fill>
-        <x:patternFill patternType="solid">
+        <x:patternFill>
           <x:bgColor rgb="FFFEE2E2"/>
         </x:patternFill>
       </x:fill>
@@ -988,7 +988,7 @@
         <x:color rgb="FF9A3412"/>
       </x:font>
       <x:fill>
-        <x:patternFill patternType="solid">
+        <x:patternFill>
           <x:bgColor rgb="FFFFEDD5"/>
         </x:patternFill>
       </x:fill>
@@ -998,7 +998,7 @@
         <x:color rgb="FF854D0E"/>
       </x:font>
       <x:fill>
-        <x:patternFill patternType="solid">
+        <x:patternFill>
           <x:bgColor rgb="FFFEF3C7"/>
         </x:patternFill>
       </x:fill>
@@ -1008,7 +1008,7 @@
         <x:color rgb="FF166534"/>
       </x:font>
       <x:fill>
-        <x:patternFill patternType="solid">
+        <x:patternFill>
           <x:bgColor rgb="FFDCFCE7"/>
         </x:patternFill>
       </x:fill>
@@ -1018,7 +1018,7 @@
         <x:color rgb="FF166534"/>
       </x:font>
       <x:fill>
-        <x:patternFill patternType="solid">
+        <x:patternFill>
           <x:bgColor rgb="FFDCFCE7"/>
         </x:patternFill>
       </x:fill>
@@ -1028,7 +1028,7 @@
         <x:color rgb="FF991B1B"/>
       </x:font>
       <x:fill>
-        <x:patternFill patternType="solid">
+        <x:patternFill>
           <x:bgColor rgb="FFFEE2E2"/>
         </x:patternFill>
       </x:fill>
@@ -1039,7 +1039,7 @@
         <x:color rgb="FF991B1B"/>
       </x:font>
       <x:fill>
-        <x:patternFill patternType="solid">
+        <x:patternFill>
           <x:bgColor rgb="FFFEE2E2"/>
         </x:patternFill>
       </x:fill>
@@ -1050,7 +1050,7 @@
         <x:color rgb="FF9A3412"/>
       </x:font>
       <x:fill>
-        <x:patternFill patternType="solid">
+        <x:patternFill>
           <x:bgColor rgb="FFFFEDD5"/>
         </x:patternFill>
       </x:fill>
@@ -1060,7 +1060,7 @@
         <x:color rgb="FF854D0E"/>
       </x:font>
       <x:fill>
-        <x:patternFill patternType="solid">
+        <x:patternFill>
           <x:bgColor rgb="FFFEF3C7"/>
         </x:patternFill>
       </x:fill>
@@ -1070,7 +1070,7 @@
         <x:color rgb="FF166534"/>
       </x:font>
       <x:fill>
-        <x:patternFill patternType="solid">
+        <x:patternFill>
           <x:bgColor rgb="FFDCFCE7"/>
         </x:patternFill>
       </x:fill>
@@ -1080,7 +1080,7 @@
         <x:color rgb="FF166534"/>
       </x:font>
       <x:fill>
-        <x:patternFill patternType="solid">
+        <x:patternFill>
           <x:bgColor rgb="FFDCFCE7"/>
         </x:patternFill>
       </x:fill>
@@ -1090,7 +1090,7 @@
         <x:color rgb="FF991B1B"/>
       </x:font>
       <x:fill>
-        <x:patternFill patternType="solid">
+        <x:patternFill>
           <x:bgColor rgb="FFFEE2E2"/>
         </x:patternFill>
       </x:fill>
@@ -1101,7 +1101,7 @@
         <x:color rgb="FF991B1B"/>
       </x:font>
       <x:fill>
-        <x:patternFill patternType="solid">
+        <x:patternFill>
           <x:bgColor rgb="FFFEE2E2"/>
         </x:patternFill>
       </x:fill>
@@ -1112,7 +1112,7 @@
         <x:color rgb="FF9A3412"/>
       </x:font>
       <x:fill>
-        <x:patternFill patternType="solid">
+        <x:patternFill>
           <x:bgColor rgb="FFFFEDD5"/>
         </x:patternFill>
       </x:fill>
@@ -1122,7 +1122,7 @@
         <x:color rgb="FF854D0E"/>
       </x:font>
       <x:fill>
-        <x:patternFill patternType="solid">
+        <x:patternFill>
           <x:bgColor rgb="FFFEF3C7"/>
         </x:patternFill>
       </x:fill>
@@ -1132,7 +1132,7 @@
         <x:color rgb="FF166534"/>
       </x:font>
       <x:fill>
-        <x:patternFill patternType="solid">
+        <x:patternFill>
           <x:bgColor rgb="FFDCFCE7"/>
         </x:patternFill>
       </x:fill>
@@ -1142,7 +1142,7 @@
         <x:color rgb="FF166534"/>
       </x:font>
       <x:fill>
-        <x:patternFill patternType="solid">
+        <x:patternFill>
           <x:bgColor rgb="FFDCFCE7"/>
         </x:patternFill>
       </x:fill>
@@ -1152,7 +1152,7 @@
         <x:color rgb="FF991B1B"/>
       </x:font>
       <x:fill>
-        <x:patternFill patternType="solid">
+        <x:patternFill>
           <x:bgColor rgb="FFFEE2E2"/>
         </x:patternFill>
       </x:fill>
@@ -1163,7 +1163,7 @@
         <x:color rgb="FF991B1B"/>
       </x:font>
       <x:fill>
-        <x:patternFill patternType="solid">
+        <x:patternFill>
           <x:bgColor rgb="FFFEE2E2"/>
         </x:patternFill>
       </x:fill>
@@ -1174,7 +1174,7 @@
         <x:color rgb="FF9A3412"/>
       </x:font>
       <x:fill>
-        <x:patternFill patternType="solid">
+        <x:patternFill>
           <x:bgColor rgb="FFFFEDD5"/>
         </x:patternFill>
       </x:fill>
@@ -1184,7 +1184,7 @@
         <x:color rgb="FF854D0E"/>
       </x:font>
       <x:fill>
-        <x:patternFill patternType="solid">
+        <x:patternFill>
           <x:bgColor rgb="FFFEF3C7"/>
         </x:patternFill>
       </x:fill>
@@ -1194,7 +1194,7 @@
         <x:color rgb="FF166534"/>
       </x:font>
       <x:fill>
-        <x:patternFill patternType="solid">
+        <x:patternFill>
           <x:bgColor rgb="FFDCFCE7"/>
         </x:patternFill>
       </x:fill>
@@ -1204,7 +1204,7 @@
         <x:color rgb="FF166534"/>
       </x:font>
       <x:fill>
-        <x:patternFill patternType="solid">
+        <x:patternFill>
           <x:bgColor rgb="FFDCFCE7"/>
         </x:patternFill>
       </x:fill>
@@ -1214,7 +1214,7 @@
         <x:color rgb="FF991B1B"/>
       </x:font>
       <x:fill>
-        <x:patternFill patternType="solid">
+        <x:patternFill>
           <x:bgColor rgb="FFFEE2E2"/>
         </x:patternFill>
       </x:fill>
@@ -1225,7 +1225,7 @@
         <x:color rgb="FF991B1B"/>
       </x:font>
       <x:fill>
-        <x:patternFill patternType="solid">
+        <x:patternFill>
           <x:bgColor rgb="FFFEE2E2"/>
         </x:patternFill>
       </x:fill>
@@ -1236,7 +1236,7 @@
         <x:color rgb="FF9A3412"/>
       </x:font>
       <x:fill>
-        <x:patternFill patternType="solid">
+        <x:patternFill>
           <x:bgColor rgb="FFFFEDD5"/>
         </x:patternFill>
       </x:fill>
@@ -1246,7 +1246,7 @@
         <x:color rgb="FF854D0E"/>
       </x:font>
       <x:fill>
-        <x:patternFill patternType="solid">
+        <x:patternFill>
           <x:bgColor rgb="FFFEF3C7"/>
         </x:patternFill>
       </x:fill>
@@ -1256,7 +1256,7 @@
         <x:color rgb="FF166534"/>
       </x:font>
       <x:fill>
-        <x:patternFill patternType="solid">
+        <x:patternFill>
           <x:bgColor rgb="FFDCFCE7"/>
         </x:patternFill>
       </x:fill>
@@ -1266,7 +1266,7 @@
         <x:color rgb="FF166534"/>
       </x:font>
       <x:fill>
-        <x:patternFill patternType="solid">
+        <x:patternFill>
           <x:bgColor rgb="FFDCFCE7"/>
         </x:patternFill>
       </x:fill>
@@ -1276,7 +1276,7 @@
         <x:color rgb="FF991B1B"/>
       </x:font>
       <x:fill>
-        <x:patternFill patternType="solid">
+        <x:patternFill>
           <x:bgColor rgb="FFFEE2E2"/>
         </x:patternFill>
       </x:fill>
@@ -1287,7 +1287,7 @@
         <x:color rgb="FF991B1B"/>
       </x:font>
       <x:fill>
-        <x:patternFill patternType="solid">
+        <x:patternFill>
           <x:bgColor rgb="FFFEE2E2"/>
         </x:patternFill>
       </x:fill>
@@ -1298,7 +1298,7 @@
         <x:color rgb="FF9A3412"/>
       </x:font>
       <x:fill>
-        <x:patternFill patternType="solid">
+        <x:patternFill>
           <x:bgColor rgb="FFFFEDD5"/>
         </x:patternFill>
       </x:fill>
@@ -1308,7 +1308,7 @@
         <x:color rgb="FF854D0E"/>
       </x:font>
       <x:fill>
-        <x:patternFill patternType="solid">
+        <x:patternFill>
           <x:bgColor rgb="FFFEF3C7"/>
         </x:patternFill>
       </x:fill>
@@ -1318,7 +1318,7 @@
         <x:color rgb="FF166534"/>
       </x:font>
       <x:fill>
-        <x:patternFill patternType="solid">
+        <x:patternFill>
           <x:bgColor rgb="FFDCFCE7"/>
         </x:patternFill>
       </x:fill>
@@ -1328,7 +1328,7 @@
         <x:color rgb="FF166534"/>
       </x:font>
       <x:fill>
-        <x:patternFill patternType="solid">
+        <x:patternFill>
           <x:bgColor rgb="FFDCFCE7"/>
         </x:patternFill>
       </x:fill>
@@ -1338,7 +1338,7 @@
         <x:color rgb="FF991B1B"/>
       </x:font>
       <x:fill>
-        <x:patternFill patternType="solid">
+        <x:patternFill>
           <x:bgColor rgb="FFFEE2E2"/>
         </x:patternFill>
       </x:fill>
@@ -1349,7 +1349,7 @@
         <x:color rgb="FF991B1B"/>
       </x:font>
       <x:fill>
-        <x:patternFill patternType="solid">
+        <x:patternFill>
           <x:bgColor rgb="FFFEE2E2"/>
         </x:patternFill>
       </x:fill>
@@ -1360,7 +1360,7 @@
         <x:color rgb="FF9A3412"/>
       </x:font>
       <x:fill>
-        <x:patternFill patternType="solid">
+        <x:patternFill>
           <x:bgColor rgb="FFFFEDD5"/>
         </x:patternFill>
       </x:fill>
@@ -1370,7 +1370,7 @@
         <x:color rgb="FF854D0E"/>
       </x:font>
       <x:fill>
-        <x:patternFill patternType="solid">
+        <x:patternFill>
           <x:bgColor rgb="FFFEF3C7"/>
         </x:patternFill>
       </x:fill>
@@ -1380,7 +1380,7 @@
         <x:color rgb="FF166534"/>
       </x:font>
       <x:fill>
-        <x:patternFill patternType="solid">
+        <x:patternFill>
           <x:bgColor rgb="FFDCFCE7"/>
         </x:patternFill>
       </x:fill>
@@ -1390,7 +1390,7 @@
         <x:color rgb="FF166534"/>
       </x:font>
       <x:fill>
-        <x:patternFill patternType="solid">
+        <x:patternFill>
           <x:bgColor rgb="FFDCFCE7"/>
         </x:patternFill>
       </x:fill>
@@ -1400,7 +1400,7 @@
         <x:color rgb="FF991B1B"/>
       </x:font>
       <x:fill>
-        <x:patternFill patternType="solid">
+        <x:patternFill>
           <x:bgColor rgb="FFFEE2E2"/>
         </x:patternFill>
       </x:fill>
@@ -1411,7 +1411,7 @@
         <x:color rgb="FF991B1B"/>
       </x:font>
       <x:fill>
-        <x:patternFill patternType="solid">
+        <x:patternFill>
           <x:bgColor rgb="FFFEE2E2"/>
         </x:patternFill>
       </x:fill>
@@ -1422,7 +1422,7 @@
         <x:color rgb="FF9A3412"/>
       </x:font>
       <x:fill>
-        <x:patternFill patternType="solid">
+        <x:patternFill>
           <x:bgColor rgb="FFFFEDD5"/>
         </x:patternFill>
       </x:fill>
@@ -1432,7 +1432,7 @@
         <x:color rgb="FF854D0E"/>
       </x:font>
       <x:fill>
-        <x:patternFill patternType="solid">
+        <x:patternFill>
           <x:bgColor rgb="FFFEF3C7"/>
         </x:patternFill>
       </x:fill>
@@ -1442,7 +1442,7 @@
         <x:color rgb="FF166534"/>
       </x:font>
       <x:fill>
-        <x:patternFill patternType="solid">
+        <x:patternFill>
           <x:bgColor rgb="FFDCFCE7"/>
         </x:patternFill>
       </x:fill>
@@ -1452,7 +1452,7 @@
         <x:color rgb="FF166534"/>
       </x:font>
       <x:fill>
-        <x:patternFill patternType="solid">
+        <x:patternFill>
           <x:bgColor rgb="FFDCFCE7"/>
         </x:patternFill>
       </x:fill>
@@ -1462,7 +1462,7 @@
         <x:color rgb="FF991B1B"/>
       </x:font>
       <x:fill>
-        <x:patternFill patternType="solid">
+        <x:patternFill>
           <x:bgColor rgb="FFFEE2E2"/>
         </x:patternFill>
       </x:fill>
@@ -1473,7 +1473,7 @@
         <x:color rgb="FF991B1B"/>
       </x:font>
       <x:fill>
-        <x:patternFill patternType="solid">
+        <x:patternFill>
           <x:bgColor rgb="FFFEE2E2"/>
         </x:patternFill>
       </x:fill>
@@ -1484,7 +1484,7 @@
         <x:color rgb="FF9A3412"/>
       </x:font>
       <x:fill>
-        <x:patternFill patternType="solid">
+        <x:patternFill>
           <x:bgColor rgb="FFFFEDD5"/>
         </x:patternFill>
       </x:fill>
@@ -1970,7 +1970,7 @@
       </xdr:xfrm>
       <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="R80ba6051d2304364"/>
+          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="Rb1339e20969e4e00"/>
         </a:graphicData>
       </a:graphic>
     </xdr:graphicFrame>
@@ -2000,7 +2000,7 @@
       </xdr:xfrm>
       <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="R8abfd95c57724ae3"/>
+          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="R6b461288313b470a"/>
         </a:graphicData>
       </a:graphic>
     </xdr:graphicFrame>
@@ -2030,7 +2030,7 @@
       </xdr:xfrm>
       <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="R23927eaf00524766"/>
+          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="R9f5e027c94b54d1b"/>
         </a:graphicData>
       </a:graphic>
     </xdr:graphicFrame>
@@ -2060,7 +2060,7 @@
       </xdr:xfrm>
       <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="R5d7b143b382e4cab"/>
+          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="R0fc8387114034166"/>
         </a:graphicData>
       </a:graphic>
     </xdr:graphicFrame>
@@ -2440,46 +2440,46 @@
     </x:row>
     <x:row r="2" ht="24" customHeight="1">
       <x:c r="A2" s="6" t="str">
-        <x:v>Step 9 | Executive view of risk, control maturity, vendor assurance, and access governance</x:v>
+        <x:v>Executive view of risk, control maturity, vendor assurance, and access governance</x:v>
       </x:c>
       <x:c r="B2" s="6" t="str">
-        <x:v>Step 9 | Executive view of risk, control maturity, vendor assurance, and access governance</x:v>
+        <x:v>Executive view of risk, control maturity, vendor assurance, and access governance</x:v>
       </x:c>
       <x:c r="C2" s="6" t="str">
-        <x:v>Step 9 | Executive view of risk, control maturity, vendor assurance, and access governance</x:v>
+        <x:v>Executive view of risk, control maturity, vendor assurance, and access governance</x:v>
       </x:c>
       <x:c r="D2" s="6" t="str">
-        <x:v>Step 9 | Executive view of risk, control maturity, vendor assurance, and access governance</x:v>
+        <x:v>Executive view of risk, control maturity, vendor assurance, and access governance</x:v>
       </x:c>
       <x:c r="E2" s="6" t="str">
-        <x:v>Step 9 | Executive view of risk, control maturity, vendor assurance, and access governance</x:v>
+        <x:v>Executive view of risk, control maturity, vendor assurance, and access governance</x:v>
       </x:c>
       <x:c r="F2" s="6" t="str">
-        <x:v>Step 9 | Executive view of risk, control maturity, vendor assurance, and access governance</x:v>
+        <x:v>Executive view of risk, control maturity, vendor assurance, and access governance</x:v>
       </x:c>
       <x:c r="G2" s="6" t="str">
-        <x:v>Step 9 | Executive view of risk, control maturity, vendor assurance, and access governance</x:v>
+        <x:v>Executive view of risk, control maturity, vendor assurance, and access governance</x:v>
       </x:c>
       <x:c r="H2" s="6" t="str">
-        <x:v>Step 9 | Executive view of risk, control maturity, vendor assurance, and access governance</x:v>
+        <x:v>Executive view of risk, control maturity, vendor assurance, and access governance</x:v>
       </x:c>
       <x:c r="I2" s="6" t="str">
-        <x:v>Step 9 | Executive view of risk, control maturity, vendor assurance, and access governance</x:v>
+        <x:v>Executive view of risk, control maturity, vendor assurance, and access governance</x:v>
       </x:c>
       <x:c r="J2" s="6" t="str">
-        <x:v>Step 9 | Executive view of risk, control maturity, vendor assurance, and access governance</x:v>
+        <x:v>Executive view of risk, control maturity, vendor assurance, and access governance</x:v>
       </x:c>
       <x:c r="K2" s="6" t="str">
-        <x:v>Step 9 | Executive view of risk, control maturity, vendor assurance, and access governance</x:v>
+        <x:v>Executive view of risk, control maturity, vendor assurance, and access governance</x:v>
       </x:c>
       <x:c r="L2" s="6" t="str">
-        <x:v>Step 9 | Executive view of risk, control maturity, vendor assurance, and access governance</x:v>
+        <x:v>Executive view of risk, control maturity, vendor assurance, and access governance</x:v>
       </x:c>
       <x:c r="M2" s="6" t="str">
-        <x:v>Step 9 | Executive view of risk, control maturity, vendor assurance, and access governance</x:v>
+        <x:v>Executive view of risk, control maturity, vendor assurance, and access governance</x:v>
       </x:c>
       <x:c r="N2" s="6" t="str">
-        <x:v>Step 9 | Executive view of risk, control maturity, vendor assurance, and access governance</x:v>
+        <x:v>Executive view of risk, control maturity, vendor assurance, and access governance</x:v>
       </x:c>
     </x:row>
     <x:row r="4">
@@ -2933,21 +2933,47 @@
     </x:row>
     <x:row r="58">
       <x:c r="A58" s="166" t="str">
-        <x:v>Portfolio disclaimer: Trainory, VitaSync, all records, metrics, findings, and decisions are fictional educational examples. Dashboard calculations update when the supporting data tabs are edited.</x:v>
-      </x:c>
-      <x:c r="B58" s="166"/>
-      <x:c r="C58" s="166"/>
-      <x:c r="D58" s="166"/>
-      <x:c r="E58" s="166"/>
-      <x:c r="F58" s="166"/>
-      <x:c r="G58" s="166"/>
-      <x:c r="H58" s="166"/>
-      <x:c r="I58" s="166"/>
-      <x:c r="J58" s="166"/>
-      <x:c r="K58" s="166"/>
-      <x:c r="L58" s="166"/>
-      <x:c r="M58" s="166"/>
-      <x:c r="N58" s="166"/>
+        <x:v>Case study note: Trainory, VitaSync, all records, metrics, findings, and decisions are fictional. Dashboard calculations update when supporting data tabs are edited.</x:v>
+      </x:c>
+      <x:c r="B58" s="166" t="str">
+        <x:v>Case study note: Trainory, VitaSync, all records, metrics, findings, and decisions are fictional. Dashboard calculations update when supporting data tabs are edited.</x:v>
+      </x:c>
+      <x:c r="C58" s="166" t="str">
+        <x:v>Case study note: Trainory, VitaSync, all records, metrics, findings, and decisions are fictional. Dashboard calculations update when supporting data tabs are edited.</x:v>
+      </x:c>
+      <x:c r="D58" s="166" t="str">
+        <x:v>Case study note: Trainory, VitaSync, all records, metrics, findings, and decisions are fictional. Dashboard calculations update when supporting data tabs are edited.</x:v>
+      </x:c>
+      <x:c r="E58" s="166" t="str">
+        <x:v>Case study note: Trainory, VitaSync, all records, metrics, findings, and decisions are fictional. Dashboard calculations update when supporting data tabs are edited.</x:v>
+      </x:c>
+      <x:c r="F58" s="166" t="str">
+        <x:v>Case study note: Trainory, VitaSync, all records, metrics, findings, and decisions are fictional. Dashboard calculations update when supporting data tabs are edited.</x:v>
+      </x:c>
+      <x:c r="G58" s="166" t="str">
+        <x:v>Case study note: Trainory, VitaSync, all records, metrics, findings, and decisions are fictional. Dashboard calculations update when supporting data tabs are edited.</x:v>
+      </x:c>
+      <x:c r="H58" s="166" t="str">
+        <x:v>Case study note: Trainory, VitaSync, all records, metrics, findings, and decisions are fictional. Dashboard calculations update when supporting data tabs are edited.</x:v>
+      </x:c>
+      <x:c r="I58" s="166" t="str">
+        <x:v>Case study note: Trainory, VitaSync, all records, metrics, findings, and decisions are fictional. Dashboard calculations update when supporting data tabs are edited.</x:v>
+      </x:c>
+      <x:c r="J58" s="166" t="str">
+        <x:v>Case study note: Trainory, VitaSync, all records, metrics, findings, and decisions are fictional. Dashboard calculations update when supporting data tabs are edited.</x:v>
+      </x:c>
+      <x:c r="K58" s="166" t="str">
+        <x:v>Case study note: Trainory, VitaSync, all records, metrics, findings, and decisions are fictional. Dashboard calculations update when supporting data tabs are edited.</x:v>
+      </x:c>
+      <x:c r="L58" s="166" t="str">
+        <x:v>Case study note: Trainory, VitaSync, all records, metrics, findings, and decisions are fictional. Dashboard calculations update when supporting data tabs are edited.</x:v>
+      </x:c>
+      <x:c r="M58" s="166" t="str">
+        <x:v>Case study note: Trainory, VitaSync, all records, metrics, findings, and decisions are fictional. Dashboard calculations update when supporting data tabs are edited.</x:v>
+      </x:c>
+      <x:c r="N58" s="166" t="str">
+        <x:v>Case study note: Trainory, VitaSync, all records, metrics, findings, and decisions are fictional. Dashboard calculations update when supporting data tabs are edited.</x:v>
+      </x:c>
     </x:row>
   </x:sheetData>
   <x:mergeCells>
@@ -3020,7 +3046,7 @@
     <x:cfRule type="containsText" dxfId="73" priority="2" operator="containsText" text="High"/>
   </x:conditionalFormatting>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <x:drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R8651b89870f24959"/>
+  <x:drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Re9db00453d884f38"/>
 </x:worksheet>
 </file>
 
@@ -3182,7 +3208,7 @@
     </x:row>
     <x:row r="8">
       <x:c r="A8" s="17" t="str">
-        <x:v>Portfolio risk reduction</x:v>
+        <x:v>Modeled risk reduction</x:v>
       </x:c>
       <x:c r="B8" s="23" t="n">
         <x:f>1-(SUM('Risk Data'!$J$5:$J$19)/SUM('Risk Data'!$F$5:$F$19))</x:f>
@@ -3544,55 +3570,55 @@
     </x:row>
     <x:row r="2" ht="24" customHeight="1">
       <x:c r="A2" s="6" t="str">
-        <x:v>Consolidated from the approved Step 3 risk register</x:v>
+        <x:v>Consolidated risk-register data</x:v>
       </x:c>
       <x:c r="B2" s="6" t="str">
-        <x:v>Consolidated from the approved Step 3 risk register</x:v>
+        <x:v>Consolidated risk-register data</x:v>
       </x:c>
       <x:c r="C2" s="6" t="str">
-        <x:v>Consolidated from the approved Step 3 risk register</x:v>
+        <x:v>Consolidated risk-register data</x:v>
       </x:c>
       <x:c r="D2" s="6" t="str">
-        <x:v>Consolidated from the approved Step 3 risk register</x:v>
+        <x:v>Consolidated risk-register data</x:v>
       </x:c>
       <x:c r="E2" s="6" t="str">
-        <x:v>Consolidated from the approved Step 3 risk register</x:v>
+        <x:v>Consolidated risk-register data</x:v>
       </x:c>
       <x:c r="F2" s="6" t="str">
-        <x:v>Consolidated from the approved Step 3 risk register</x:v>
+        <x:v>Consolidated risk-register data</x:v>
       </x:c>
       <x:c r="G2" s="6" t="str">
-        <x:v>Consolidated from the approved Step 3 risk register</x:v>
+        <x:v>Consolidated risk-register data</x:v>
       </x:c>
       <x:c r="H2" s="6" t="str">
-        <x:v>Consolidated from the approved Step 3 risk register</x:v>
+        <x:v>Consolidated risk-register data</x:v>
       </x:c>
       <x:c r="I2" s="6" t="str">
-        <x:v>Consolidated from the approved Step 3 risk register</x:v>
+        <x:v>Consolidated risk-register data</x:v>
       </x:c>
       <x:c r="J2" s="6" t="str">
-        <x:v>Consolidated from the approved Step 3 risk register</x:v>
+        <x:v>Consolidated risk-register data</x:v>
       </x:c>
       <x:c r="K2" s="6" t="str">
-        <x:v>Consolidated from the approved Step 3 risk register</x:v>
+        <x:v>Consolidated risk-register data</x:v>
       </x:c>
       <x:c r="L2" s="6" t="str">
-        <x:v>Consolidated from the approved Step 3 risk register</x:v>
+        <x:v>Consolidated risk-register data</x:v>
       </x:c>
       <x:c r="M2" s="6" t="str">
-        <x:v>Consolidated from the approved Step 3 risk register</x:v>
+        <x:v>Consolidated risk-register data</x:v>
       </x:c>
       <x:c r="N2" s="6" t="str">
-        <x:v>Consolidated from the approved Step 3 risk register</x:v>
+        <x:v>Consolidated risk-register data</x:v>
       </x:c>
       <x:c r="O2" s="6" t="str">
-        <x:v>Consolidated from the approved Step 3 risk register</x:v>
+        <x:v>Consolidated risk-register data</x:v>
       </x:c>
       <x:c r="P2" s="6" t="str">
-        <x:v>Consolidated from the approved Step 3 risk register</x:v>
+        <x:v>Consolidated risk-register data</x:v>
       </x:c>
       <x:c r="Q2" s="6" t="str">
-        <x:v>Consolidated from the approved Step 3 risk register</x:v>
+        <x:v>Consolidated risk-register data</x:v>
       </x:c>
     </x:row>
     <x:row r="4" ht="34" customHeight="1">
@@ -4481,7 +4507,7 @@
   </x:conditionalFormatting>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rc772f82c47434ca2"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R3610b99e3d2843d3"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -4536,34 +4562,34 @@
     </x:row>
     <x:row r="2" ht="24" customHeight="1">
       <x:c r="A2" s="6" t="str">
-        <x:v>Consolidated from the approved Step 4 NIST CSF 2.0 assessment</x:v>
+        <x:v>Consolidated NIST CSF 2.0 assessment data</x:v>
       </x:c>
       <x:c r="B2" s="6" t="str">
-        <x:v>Consolidated from the approved Step 4 NIST CSF 2.0 assessment</x:v>
+        <x:v>Consolidated NIST CSF 2.0 assessment data</x:v>
       </x:c>
       <x:c r="C2" s="6" t="str">
-        <x:v>Consolidated from the approved Step 4 NIST CSF 2.0 assessment</x:v>
+        <x:v>Consolidated NIST CSF 2.0 assessment data</x:v>
       </x:c>
       <x:c r="D2" s="6" t="str">
-        <x:v>Consolidated from the approved Step 4 NIST CSF 2.0 assessment</x:v>
+        <x:v>Consolidated NIST CSF 2.0 assessment data</x:v>
       </x:c>
       <x:c r="E2" s="6" t="str">
-        <x:v>Consolidated from the approved Step 4 NIST CSF 2.0 assessment</x:v>
+        <x:v>Consolidated NIST CSF 2.0 assessment data</x:v>
       </x:c>
       <x:c r="F2" s="6" t="str">
-        <x:v>Consolidated from the approved Step 4 NIST CSF 2.0 assessment</x:v>
+        <x:v>Consolidated NIST CSF 2.0 assessment data</x:v>
       </x:c>
       <x:c r="G2" s="6" t="str">
-        <x:v>Consolidated from the approved Step 4 NIST CSF 2.0 assessment</x:v>
+        <x:v>Consolidated NIST CSF 2.0 assessment data</x:v>
       </x:c>
       <x:c r="H2" s="6" t="str">
-        <x:v>Consolidated from the approved Step 4 NIST CSF 2.0 assessment</x:v>
+        <x:v>Consolidated NIST CSF 2.0 assessment data</x:v>
       </x:c>
       <x:c r="I2" s="6" t="str">
-        <x:v>Consolidated from the approved Step 4 NIST CSF 2.0 assessment</x:v>
+        <x:v>Consolidated NIST CSF 2.0 assessment data</x:v>
       </x:c>
       <x:c r="J2" s="6" t="str">
-        <x:v>Consolidated from the approved Step 4 NIST CSF 2.0 assessment</x:v>
+        <x:v>Consolidated NIST CSF 2.0 assessment data</x:v>
       </x:c>
     </x:row>
     <x:row r="4" ht="34" customHeight="1">
@@ -5325,7 +5351,7 @@
   </x:conditionalFormatting>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R8dca64c5eb564bb2"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Redd2c9157b2f42cb"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -5392,43 +5418,43 @@
     </x:row>
     <x:row r="2" ht="24" customHeight="1">
       <x:c r="A2" s="6" t="str">
-        <x:v>Control-level analytics from the approved Step 7 VitaSync assessment</x:v>
+        <x:v>Control-level analytics from the VitaSync vendor assessment</x:v>
       </x:c>
       <x:c r="B2" s="6" t="str">
-        <x:v>Control-level analytics from the approved Step 7 VitaSync assessment</x:v>
+        <x:v>Control-level analytics from the VitaSync vendor assessment</x:v>
       </x:c>
       <x:c r="C2" s="6" t="str">
-        <x:v>Control-level analytics from the approved Step 7 VitaSync assessment</x:v>
+        <x:v>Control-level analytics from the VitaSync vendor assessment</x:v>
       </x:c>
       <x:c r="D2" s="6" t="str">
-        <x:v>Control-level analytics from the approved Step 7 VitaSync assessment</x:v>
+        <x:v>Control-level analytics from the VitaSync vendor assessment</x:v>
       </x:c>
       <x:c r="E2" s="6" t="str">
-        <x:v>Control-level analytics from the approved Step 7 VitaSync assessment</x:v>
+        <x:v>Control-level analytics from the VitaSync vendor assessment</x:v>
       </x:c>
       <x:c r="F2" s="6" t="str">
-        <x:v>Control-level analytics from the approved Step 7 VitaSync assessment</x:v>
+        <x:v>Control-level analytics from the VitaSync vendor assessment</x:v>
       </x:c>
       <x:c r="G2" s="6" t="str">
-        <x:v>Control-level analytics from the approved Step 7 VitaSync assessment</x:v>
+        <x:v>Control-level analytics from the VitaSync vendor assessment</x:v>
       </x:c>
       <x:c r="H2" s="6" t="str">
-        <x:v>Control-level analytics from the approved Step 7 VitaSync assessment</x:v>
+        <x:v>Control-level analytics from the VitaSync vendor assessment</x:v>
       </x:c>
       <x:c r="I2" s="6" t="str">
-        <x:v>Control-level analytics from the approved Step 7 VitaSync assessment</x:v>
+        <x:v>Control-level analytics from the VitaSync vendor assessment</x:v>
       </x:c>
       <x:c r="J2" s="6" t="str">
-        <x:v>Control-level analytics from the approved Step 7 VitaSync assessment</x:v>
+        <x:v>Control-level analytics from the VitaSync vendor assessment</x:v>
       </x:c>
       <x:c r="K2" s="6" t="str">
-        <x:v>Control-level analytics from the approved Step 7 VitaSync assessment</x:v>
+        <x:v>Control-level analytics from the VitaSync vendor assessment</x:v>
       </x:c>
       <x:c r="L2" s="6" t="str">
-        <x:v>Control-level analytics from the approved Step 7 VitaSync assessment</x:v>
+        <x:v>Control-level analytics from the VitaSync vendor assessment</x:v>
       </x:c>
       <x:c r="M2" s="6" t="str">
-        <x:v>Control-level analytics from the approved Step 7 VitaSync assessment</x:v>
+        <x:v>Control-level analytics from the VitaSync vendor assessment</x:v>
       </x:c>
     </x:row>
     <x:row r="4" ht="34" customHeight="1">
@@ -6520,7 +6546,7 @@
   </x:conditionalFormatting>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R5d7edf3cc5544650"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Ra9af5b672cf740e3"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -6595,49 +6621,49 @@
     </x:row>
     <x:row r="2" ht="24" customHeight="1">
       <x:c r="A2" s="6" t="str">
-        <x:v>Decision-level analytics from the approved Step 8 quarterly access review</x:v>
+        <x:v>Decision-level analytics from the quarterly access review</x:v>
       </x:c>
       <x:c r="B2" s="6" t="str">
-        <x:v>Decision-level analytics from the approved Step 8 quarterly access review</x:v>
+        <x:v>Decision-level analytics from the quarterly access review</x:v>
       </x:c>
       <x:c r="C2" s="6" t="str">
-        <x:v>Decision-level analytics from the approved Step 8 quarterly access review</x:v>
+        <x:v>Decision-level analytics from the quarterly access review</x:v>
       </x:c>
       <x:c r="D2" s="6" t="str">
-        <x:v>Decision-level analytics from the approved Step 8 quarterly access review</x:v>
+        <x:v>Decision-level analytics from the quarterly access review</x:v>
       </x:c>
       <x:c r="E2" s="6" t="str">
-        <x:v>Decision-level analytics from the approved Step 8 quarterly access review</x:v>
+        <x:v>Decision-level analytics from the quarterly access review</x:v>
       </x:c>
       <x:c r="F2" s="6" t="str">
-        <x:v>Decision-level analytics from the approved Step 8 quarterly access review</x:v>
+        <x:v>Decision-level analytics from the quarterly access review</x:v>
       </x:c>
       <x:c r="G2" s="6" t="str">
-        <x:v>Decision-level analytics from the approved Step 8 quarterly access review</x:v>
+        <x:v>Decision-level analytics from the quarterly access review</x:v>
       </x:c>
       <x:c r="H2" s="6" t="str">
-        <x:v>Decision-level analytics from the approved Step 8 quarterly access review</x:v>
+        <x:v>Decision-level analytics from the quarterly access review</x:v>
       </x:c>
       <x:c r="I2" s="6" t="str">
-        <x:v>Decision-level analytics from the approved Step 8 quarterly access review</x:v>
+        <x:v>Decision-level analytics from the quarterly access review</x:v>
       </x:c>
       <x:c r="J2" s="6" t="str">
-        <x:v>Decision-level analytics from the approved Step 8 quarterly access review</x:v>
+        <x:v>Decision-level analytics from the quarterly access review</x:v>
       </x:c>
       <x:c r="K2" s="6" t="str">
-        <x:v>Decision-level analytics from the approved Step 8 quarterly access review</x:v>
+        <x:v>Decision-level analytics from the quarterly access review</x:v>
       </x:c>
       <x:c r="L2" s="6" t="str">
-        <x:v>Decision-level analytics from the approved Step 8 quarterly access review</x:v>
+        <x:v>Decision-level analytics from the quarterly access review</x:v>
       </x:c>
       <x:c r="M2" s="6" t="str">
-        <x:v>Decision-level analytics from the approved Step 8 quarterly access review</x:v>
+        <x:v>Decision-level analytics from the quarterly access review</x:v>
       </x:c>
       <x:c r="N2" s="6" t="str">
-        <x:v>Decision-level analytics from the approved Step 8 quarterly access review</x:v>
+        <x:v>Decision-level analytics from the quarterly access review</x:v>
       </x:c>
       <x:c r="O2" s="6" t="str">
-        <x:v>Decision-level analytics from the approved Step 8 quarterly access review</x:v>
+        <x:v>Decision-level analytics from the quarterly access review</x:v>
       </x:c>
     </x:row>
     <x:row r="4" ht="34" customHeight="1">
@@ -8004,7 +8030,7 @@
   </x:conditionalFormatting>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R3fdf3a6bf4dd4001"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R35ae9d703ae54e7c"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -8808,7 +8834,7 @@
   </x:conditionalFormatting>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R7e6bf37f5cee4520"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R2e87cef8db7d473a"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -8827,47 +8853,47 @@
   <x:sheetData>
     <x:row r="1" ht="32" customHeight="1">
       <x:c r="A1" s="3" t="str">
-        <x:v>Trainory | Dashboard Guide</x:v>
+        <x:v>Trainory Dashboard Methodology</x:v>
       </x:c>
       <x:c r="B1" s="3" t="str">
-        <x:v>Trainory | Dashboard Guide</x:v>
+        <x:v>Trainory Dashboard Methodology</x:v>
       </x:c>
       <x:c r="C1" s="3" t="str">
-        <x:v>Trainory | Dashboard Guide</x:v>
+        <x:v>Trainory Dashboard Methodology</x:v>
       </x:c>
       <x:c r="D1" s="3" t="str">
-        <x:v>Trainory | Dashboard Guide</x:v>
+        <x:v>Trainory Dashboard Methodology</x:v>
       </x:c>
       <x:c r="E1" s="3" t="str">
-        <x:v>Trainory | Dashboard Guide</x:v>
+        <x:v>Trainory Dashboard Methodology</x:v>
       </x:c>
       <x:c r="F1" s="3" t="str">
-        <x:v>Trainory | Dashboard Guide</x:v>
+        <x:v>Trainory Dashboard Methodology</x:v>
       </x:c>
     </x:row>
     <x:row r="2" ht="24" customHeight="1">
       <x:c r="A2" s="6" t="str">
-        <x:v>How to use and explain the Step 9 analytics artifact</x:v>
+        <x:v>Metric definitions, source data, and calculation methodology</x:v>
       </x:c>
       <x:c r="B2" s="6" t="str">
-        <x:v>How to use and explain the Step 9 analytics artifact</x:v>
+        <x:v>Metric definitions, source data, and calculation methodology</x:v>
       </x:c>
       <x:c r="C2" s="6" t="str">
-        <x:v>How to use and explain the Step 9 analytics artifact</x:v>
+        <x:v>Metric definitions, source data, and calculation methodology</x:v>
       </x:c>
       <x:c r="D2" s="6" t="str">
-        <x:v>How to use and explain the Step 9 analytics artifact</x:v>
+        <x:v>Metric definitions, source data, and calculation methodology</x:v>
       </x:c>
       <x:c r="E2" s="6" t="str">
-        <x:v>How to use and explain the Step 9 analytics artifact</x:v>
+        <x:v>Metric definitions, source data, and calculation methodology</x:v>
       </x:c>
       <x:c r="F2" s="6" t="str">
-        <x:v>How to use and explain the Step 9 analytics artifact</x:v>
+        <x:v>Metric definitions, source data, and calculation methodology</x:v>
       </x:c>
     </x:row>
     <x:row r="4">
       <x:c r="A4" s="8" t="str">
-        <x:v>WHAT THIS WORKBOOK DEMONSTRATES</x:v>
+        <x:v>PURPOSE</x:v>
       </x:c>
       <x:c r="B4" s="8"/>
       <x:c r="C4" s="8"/>
@@ -8877,7 +8903,7 @@
     </x:row>
     <x:row r="5">
       <x:c r="A5" s="185" t="str">
-        <x:v>This workbook consolidates Trainory's approved risk register, NIST CSF assessment, vendor-risk assessment, and access review into one executive reporting layer. It demonstrates data normalization, formula-driven KPIs, cross-functional findings analysis, prioritization, and communication of technical risk to leadership.</x:v>
+        <x:v>Summarizes risk, access-review, vendor, and NIST CSF data for management review.</x:v>
       </x:c>
       <x:c r="B5" s="186"/>
       <x:c r="C5" s="186"/>
@@ -8903,7 +8929,7 @@
     </x:row>
     <x:row r="9">
       <x:c r="A9" s="8" t="str">
-        <x:v>SUGGESTED REVIEW SEQUENCE</x:v>
+        <x:v>DASHBOARD STRUCTURE</x:v>
       </x:c>
       <x:c r="B9" s="8"/>
       <x:c r="C9" s="8"/>
@@ -8917,7 +8943,7 @@
       </x:c>
       <x:c r="B10" s="12"/>
       <x:c r="C10" s="12" t="str">
-        <x:v>What to explain</x:v>
+        <x:v>Content</x:v>
       </x:c>
       <x:c r="D10" s="12"/>
       <x:c r="E10" s="12"/>
@@ -8929,7 +8955,7 @@
       </x:c>
       <x:c r="B11" s="144"/>
       <x:c r="C11" s="144" t="str">
-        <x:v>Start with the six core signals: risk exposure, control maturity, vendor assurance, findings, access exceptions, and risk reduction.</x:v>
+        <x:v>Six core signals: risk exposure, control maturity, vendor assurance, findings, access exceptions, and risk reduction.</x:v>
       </x:c>
       <x:c r="D11" s="144"/>
       <x:c r="E11" s="144"/>
@@ -8941,7 +8967,7 @@
       </x:c>
       <x:c r="B12" s="144"/>
       <x:c r="C12" s="144" t="str">
-        <x:v>Explain where residual risk remains after considering current controls.</x:v>
+        <x:v>Residual risk remaining after current controls.</x:v>
       </x:c>
       <x:c r="D12" s="144"/>
       <x:c r="E12" s="144"/>
@@ -8953,7 +8979,7 @@
       </x:c>
       <x:c r="B13" s="144"/>
       <x:c r="C13" s="144" t="str">
-        <x:v>Show how Implemented, Partial, and Not Implemented statuses become a consistent maturity score.</x:v>
+        <x:v>Conversion of Implemented, Partial, and Not Implemented statuses into a maturity score.</x:v>
       </x:c>
       <x:c r="D13" s="144"/>
       <x:c r="E13" s="144"/>
@@ -8965,7 +8991,7 @@
       </x:c>
       <x:c r="B14" s="144"/>
       <x:c r="C14" s="144" t="str">
-        <x:v>Connect assessment gaps to assigned owners, corrective actions, deadlines, and residual risk.</x:v>
+        <x:v>Assessment gaps, owners, corrective actions, deadlines, and residual risk.</x:v>
       </x:c>
       <x:c r="D14" s="144"/>
       <x:c r="E14" s="144"/>
@@ -8977,16 +9003,14 @@
       </x:c>
       <x:c r="B15" s="144"/>
       <x:c r="C15" s="144" t="str">
-        <x:v>Open the data tabs to show that every KPI and chart is traceable to individual records.</x:v>
+        <x:v>Record-level data supporting each KPI and chart.</x:v>
       </x:c>
       <x:c r="D15" s="144"/>
       <x:c r="E15" s="144"/>
       <x:c r="F15" s="144"/>
     </x:row>
     <x:row r="18">
-      <x:c r="A18" s="8" t="str">
-        <x:v>INTERVIEW-READY EXPLANATION</x:v>
-      </x:c>
+      <x:c r="A18" s="8"/>
       <x:c r="B18" s="8"/>
       <x:c r="C18" s="8"/>
       <x:c r="D18" s="8"/>
@@ -8994,9 +9018,7 @@
       <x:c r="F18" s="8"/>
     </x:row>
     <x:row r="19">
-      <x:c r="A19" s="158" t="str">
-        <x:v>I created a consolidated GRC dashboard for a fictional fitness-technology company. I normalized information from the risk register, NIST CSF assessment, vendor review, and quarterly access certification. I then used formulas to calculate residual-risk concentration, control maturity, vendor assurance, access exceptions, and open findings. The charts help leadership see where exposure is concentrated, while the priority table connects each issue to an owner and remediation status. I kept the calculation layer visible so every number can be traced back to a source record.</x:v>
-      </x:c>
+      <x:c r="A19" s="158"/>
       <x:c r="B19" s="159"/>
       <x:c r="C19" s="159"/>
       <x:c r="D19" s="159"/>
@@ -9119,7 +9141,7 @@
     </x:row>
     <x:row r="34">
       <x:c r="A34" s="202" t="str">
-        <x:v>Portfolio disclaimer: all organizations, people, records, findings, and decisions are fictional. This workbook is an educational GRC and data-analytics artifact, not an audit opinion or production risk report.</x:v>
+        <x:v>Case study note: Trainory and all assessment data are fictional.</x:v>
       </x:c>
       <x:c r="B34" s="202"/>
       <x:c r="C34" s="202"/>
